--- a/artfynd/A 31242-2022 artfynd.xlsx
+++ b/artfynd/A 31242-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31242-2022 artfynd.xlsx
+++ b/artfynd/A 31242-2022 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>292873</v>
+        <v>920736</v>
       </c>
       <c r="B2" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>870621.1094055772</v>
+        <v>870528</v>
       </c>
       <c r="R2" t="n">
-        <v>7496798.249943583</v>
+        <v>7496584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,42 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>920736</v>
+        <v>292873</v>
       </c>
       <c r="B3" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870528.2039257633</v>
+        <v>870621</v>
       </c>
       <c r="R3" t="n">
-        <v>7496583.950409413</v>
+        <v>7496798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2009-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 31242-2022 artfynd.xlsx
+++ b/artfynd/A 31242-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/292873</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/920736</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>